--- a/frases.xlsx
+++ b/frases.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Master BD ENyD\10-TFM\github\political_sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6153B89F-91CD-4005-970C-1182172D13DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BF4A01-526A-4F95-877F-25EE9E6A1C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11295" xr2:uid="{0F93FE12-E7F2-438A-9208-09858008CB97}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{0F93FE12-E7F2-438A-9208-09858008CB97}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$C$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>score</t>
   </si>
@@ -84,6 +84,63 @@
   </si>
   <si>
     <t>lr</t>
+  </si>
+  <si>
+    <t>La Pasionaria y Santiago Carrillo son sus referentes</t>
+  </si>
+  <si>
+    <t>Se sabe de principio a fin la letra de La Internacional</t>
+  </si>
+  <si>
+    <t>Adora a Perro Santxe</t>
+  </si>
+  <si>
+    <t>San Zapatero es la fiesta que nunca deja pasar</t>
+  </si>
+  <si>
+    <t>Sí se puede sí se puede.</t>
+  </si>
+  <si>
+    <t>Se ha dejado coleta a lo Pablo Iglesias</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Rajoy es un patriota y Aznar un estratega</t>
+  </si>
+  <si>
+    <t>Que el PP se ha financiado ilegalmente es un bulo</t>
+  </si>
+  <si>
+    <t>Cada vez que habla Ayuso pido callar a todo el mundo. Dice unas cosas …....</t>
+  </si>
+  <si>
+    <t>Pa que roben todos que sean los mios</t>
+  </si>
+  <si>
+    <t>Soy Facha…que pasa!!</t>
+  </si>
+  <si>
+    <t>La inmigración es una amenaza a lo español</t>
+  </si>
+  <si>
+    <t>Los catalanes son unos insolidarios</t>
+  </si>
+  <si>
+    <t>El gobierno es comunista, bolivariano y  todo eso..</t>
+  </si>
+  <si>
+    <t>Viva el vino!!</t>
+  </si>
+  <si>
+    <t>Me va ustezzzzzz a desí. cuantah copitah de vino me pued tomarrrr</t>
+  </si>
+  <si>
+    <t>En Iraq hay armas de destruccion másiva. Creame usted</t>
+  </si>
+  <si>
+    <t>Soy Mr Handsome, que pasa!!</t>
   </si>
 </sst>
 </file>
@@ -456,7 +513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39405FDD-D5E9-46E4-9A3E-93FCEB184B26}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="69.42578125" bestFit="1" customWidth="1"/>
@@ -495,7 +552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -506,7 +563,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -517,7 +574,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -530,7 +587,7 @@
     </row>
     <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -539,7 +596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -552,7 +609,7 @@
     </row>
     <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -561,7 +618,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -583,11 +640,209 @@
         <v>13</v>
       </c>
     </row>
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <v>999</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>999</v>
+      </c>
+      <c r="C27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28">
+        <v>999</v>
+      </c>
+      <c r="C28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>999</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C11" xr:uid="{39405FDD-D5E9-46E4-9A3E-93FCEB184B26}">
-    <filterColumn colId="0">
+  <autoFilter ref="A1:C25" xr:uid="{39405FDD-D5E9-46E4-9A3E-93FCEB184B26}">
+    <filterColumn colId="1">
       <filters>
-        <filter val="L"/>
+        <filter val="999"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/frases.xlsx
+++ b/frases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Master BD ENyD\10-TFM\github\political_sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BF4A01-526A-4F95-877F-25EE9E6A1C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61AEA7C-9694-40D0-9A0E-78160B9DD9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{0F93FE12-E7F2-438A-9208-09858008CB97}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{0F93FE12-E7F2-438A-9208-09858008CB97}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>R</t>
   </si>
   <si>
-    <t>Es usted un revolucionario peligroso? Es broma…Izquierda</t>
-  </si>
-  <si>
     <t>usted nació siendo de izquierdas y hasta la tumba</t>
   </si>
   <si>
@@ -141,6 +138,9 @@
   </si>
   <si>
     <t>Soy Mr Handsome, que pasa!!</t>
+  </si>
+  <si>
+    <t>Es usted un revolucionario peligroso? Es broma…</t>
   </si>
 </sst>
 </file>
@@ -512,7 +512,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39405FDD-D5E9-46E4-9A3E-93FCEB184B26}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -521,7 +520,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -538,7 +537,7 @@
         <v>999</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -549,7 +548,7 @@
         <v>999</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -560,7 +559,7 @@
         <v>999</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -571,10 +570,10 @@
         <v>999</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -582,21 +581,21 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -604,43 +603,43 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -648,21 +647,21 @@
         <v>2</v>
       </c>
       <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -670,43 +669,43 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
+      </c>
+      <c r="C17" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17">
-        <v>3</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -714,43 +713,43 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20">
-        <v>3</v>
-      </c>
-      <c r="C20" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -758,40 +757,40 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24">
-        <v>3</v>
-      </c>
-      <c r="C24" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
-      </c>
-      <c r="C25" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -802,7 +801,7 @@
         <v>999</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -813,7 +812,7 @@
         <v>999</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -824,7 +823,7 @@
         <v>999</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -835,17 +834,10 @@
         <v>999</v>
       </c>
       <c r="C29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C25" xr:uid="{39405FDD-D5E9-46E4-9A3E-93FCEB184B26}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="999"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>